--- a/artfynd/A 5634-2025 artfynd.xlsx
+++ b/artfynd/A 5634-2025 artfynd.xlsx
@@ -790,12 +790,7 @@
         <v>90030264</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>305450.8697466446</v>
+        <v>305451</v>
       </c>
       <c r="R3" t="n">
-        <v>6458788.367062571</v>
+        <v>6458788</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -860,19 +855,9 @@
           <t>1997-08-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1997-08-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 5634-2025 artfynd.xlsx
+++ b/artfynd/A 5634-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>90030264</v>
       </c>
       <c r="B3" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5634-2025 artfynd.xlsx
+++ b/artfynd/A 5634-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>90030264</v>
       </c>
       <c r="B3" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5634-2025 artfynd.xlsx
+++ b/artfynd/A 5634-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>90030264</v>
       </c>
       <c r="B3" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5634-2025 artfynd.xlsx
+++ b/artfynd/A 5634-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>90030264</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5634-2025 artfynd.xlsx
+++ b/artfynd/A 5634-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>90030264</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5634-2025 artfynd.xlsx
+++ b/artfynd/A 5634-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>90030264</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5634-2025 artfynd.xlsx
+++ b/artfynd/A 5634-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>90030264</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5634-2025 artfynd.xlsx
+++ b/artfynd/A 5634-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>90030264</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5634-2025 artfynd.xlsx
+++ b/artfynd/A 5634-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>90030264</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5634-2025 artfynd.xlsx
+++ b/artfynd/A 5634-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>90030264</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5634-2025 artfynd.xlsx
+++ b/artfynd/A 5634-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>90030264</v>
       </c>
       <c r="B3" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5634-2025 artfynd.xlsx
+++ b/artfynd/A 5634-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>2996307</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>305445.8657095734</v>
+        <v>305446</v>
       </c>
       <c r="R2" t="n">
-        <v>6458783.338157766</v>
+        <v>6458783</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>1997-08-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1997-08-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90030264</v>
+        <v>88476583</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,20 +800,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>200 m SSO om vägskälet väg 160 och Torpvägen, innanför branten, Boh</t>
+          <t>Avfart mot Granbua, 100 m åt NNO, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>305451</v>
+        <v>305433</v>
       </c>
       <c r="R3" t="n">
-        <v>6458788</v>
+        <v>6458663</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,19 +847,19 @@
           <t>Röra</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>OB-Oru-1853</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1997-08-03</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1997-08-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bohusläns flora - 2011.</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,13 +868,14 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Evastina Blomgren</t>
+          <t>Olle Molander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -887,7 +885,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Bohusläns Flora 2011</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 5634-2025 artfynd.xlsx
+++ b/artfynd/A 5634-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2996307</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,8 +898,17 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88476583</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>